--- a/assets/constructions/examples/ctd_tmf_module.xlsx
+++ b/assets/constructions/examples/ctd_tmf_module.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -699,11 +719,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>252.63</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>23225.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GVNAL26-T5.5C</t>
+          <t>GVNAR29-T6.5-1C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -718,7 +752,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VAR_GVNA_26</t>
+          <t>VAR_GVNA_29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -739,12 +773,12 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCL</t>
+          <t>VARGUS_VG_CUT_HPCR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:26L</t>
+          <t>VARGUS_GVN:29R</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -755,7 +789,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -768,19 +802,19 @@
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>6.35</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>15.55</v>
+        <v>14.25</v>
       </c>
       <c r="V3" t="n">
         <v>32</v>
@@ -813,6 +847,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>252.63</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>23225.21</v>
       </c>
     </row>
     <row r="4">
@@ -929,6 +977,20 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>252.63</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>23225.21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1044,11 +1106,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>242.88</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>22328.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GVNAR29-T6.5-1C</t>
+          <t>GVNAL29-T6.5-2C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1084,12 +1160,12 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCR</t>
+          <t>VARGUS_VG_CUT_HPCL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:29R</t>
+          <t>VARGUS_GVN:29L</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1100,7 +1176,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1158,6 +1234,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>252.63</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>23225.21</v>
       </c>
     </row>
   </sheetData>
